--- a/data/Escenarios_Gx/320kW_4dias/elmo_data.xlsx
+++ b/data/Escenarios_Gx/320kW_4dias/elmo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\320kW_4dias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D40118-0673-4031-8629-78272D06B615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60543E8A-360B-4CF7-A59C-653E671FE4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -558,9 +558,6 @@
     <t>Sandvik</t>
   </si>
   <si>
-    <t>p_max_ssee</t>
-  </si>
-  <si>
     <t>charge_time</t>
   </si>
   <si>
@@ -646,6 +643,9 @@
   </si>
   <si>
     <t>electric</t>
+  </si>
+  <si>
+    <t>c_inv_ssee</t>
   </si>
 </sst>
 </file>
@@ -1571,7 +1571,7 @@
         <v>62</v>
       </c>
       <c r="AE1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1680,7 +1680,7 @@
         <v>161</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>52</v>
@@ -1775,7 +1775,7 @@
         <v>161</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>52</v>
@@ -1870,7 +1870,7 @@
         <v>161</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="20" t="s">
         <v>52</v>
@@ -1965,7 +1965,7 @@
         <v>161</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>52</v>
@@ -2076,22 +2076,22 @@
         <v>162</v>
       </c>
       <c r="C1" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="G1" s="12" t="s">
-        <v>194</v>
-      </c>
       <c r="H1" s="12" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2117,7 +2117,7 @@
         <v>51</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>34</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2128,13 +2128,13 @@
         <v>165</v>
       </c>
       <c r="C3" s="35">
-        <v>35722</v>
+        <v>219495</v>
       </c>
       <c r="D3" s="28">
-        <v>38221</v>
+        <v>234851</v>
       </c>
       <c r="E3" s="20">
-        <v>5733</v>
+        <v>35228</v>
       </c>
       <c r="F3" s="30">
         <v>2</v>
@@ -2143,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="35">
-        <v>1500</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2205,8 +2205,7 @@
         <v>171</v>
       </c>
       <c r="C3" s="35">
-        <f>2*21038</f>
-        <v>42076</v>
+        <v>320000</v>
       </c>
       <c r="D3" s="28">
         <v>320</v>
@@ -7214,19 +7213,19 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -7240,10 +7239,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>34</v>
@@ -7257,13 +7256,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="D3" s="3">
-        <v>30.8</v>
+        <v>350</v>
       </c>
       <c r="E3" s="4">
         <v>6.9</v>
@@ -7280,13 +7279,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>184</v>
-      </c>
       <c r="D4" s="3">
-        <v>119</v>
+        <v>1189</v>
       </c>
       <c r="E4" s="4">
         <v>21.6</v>
@@ -7316,25 +7315,25 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="H1" s="57" t="s">
-        <v>187</v>
-      </c>
       <c r="I1" s="58" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -7348,7 +7347,7 @@
         <v>163</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>34</v>
@@ -7371,10 +7370,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C3" s="4">
-        <v>18308</v>
+        <v>326000</v>
       </c>
       <c r="D3" s="3">
         <v>2900</v>
@@ -7417,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="57" t="s">
         <v>196</v>
       </c>
-      <c r="D1" s="57" t="s">
+      <c r="E1" s="58" t="s">
         <v>197</v>
-      </c>
-      <c r="E1" s="58" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -7443,7 +7442,7 @@
         <v>163</v>
       </c>
       <c r="E2" s="58" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
